--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6539-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6539-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CC04476-5029-4CDE-B3B0-2A879E2EB408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6AE00C88-8E4E-444A-9D3D-3EFAC4D874D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{49E2F78C-3376-4749-B7FE-68DC5BA0480C}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{12D755FA-6FB5-4B69-B291-BAC919EDB58B}"/>
   </bookViews>
   <sheets>
     <sheet name="6539-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1550,30 +1550,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{391FB143-4C27-4D06-9A4D-83F6AFA046C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD820D89-22D4-4BB8-8CEC-6066DDE85D45}">
   <dimension ref="A1:X28"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="8.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="8.125" customWidth="1"/>
-    <col min="24" max="24" width="8" customWidth="1"/>
+    <col min="1" max="1" width="3.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1607,7 +1607,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1643,7 +1643,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1763,7 +1763,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="41">
         <v>2024</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>9.67</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="43" t="s">
         <v>29</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>7.13</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="44"/>
       <c r="B10" s="44"/>
       <c r="C10" s="20" t="s">
@@ -2157,7 +2157,7 @@
       <c r="W10" s="50"/>
       <c r="X10" s="46"/>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2023</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="41">
         <v>2022</v>
       </c>
@@ -2523,7 +2523,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2671,7 +2671,7 @@
         <v>4.37</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2021</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>8.59</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>5.93</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2891,7 +2891,7 @@
         <v>2.66</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="41">
         <v>2020</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>7.09</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="51">
         <v>2019</v>
       </c>
@@ -3035,7 +3035,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="53"/>
       <c r="B23" s="54"/>
       <c r="C23" s="22" t="s">
@@ -3063,7 +3063,7 @@
       <c r="W23" s="60"/>
       <c r="X23" s="56"/>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="41">
         <v>2018</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="39">
         <v>2017</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="41">
         <v>2016</v>
       </c>
@@ -3279,7 +3279,7 @@
         <v>4.34</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="39">
         <v>2015</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>5.07</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="41" t="s">
         <v>49</v>
       </c>
